--- a/游戏机制/生物生成/所有生物的spawnRules.xlsx
+++ b/游戏机制/生物生成/所有生物的spawnRules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\生物生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8E8686-0A01-40C1-B207-1C6FE66FDFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D5E50F-99CA-4137-9E07-78B088A1769E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1072,12 +1072,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1087,13 +1081,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1101,6 +1089,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1696,10 +1696,10 @@
       <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>206</v>
       </c>
     </row>
@@ -1713,23 +1713,23 @@
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>213</v>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="19" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1760,7 +1760,7 @@
       <c r="C10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16"/>
+      <c r="D10" s="19"/>
       <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
@@ -1775,7 +1775,7 @@
       <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="19" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -1792,7 +1792,7 @@
       <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="16"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
@@ -1807,7 +1807,7 @@
       <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="19"/>
       <c r="E13" s="7" t="s">
         <v>27</v>
       </c>
@@ -1833,7 +1833,7 @@
       <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1842,7 +1842,7 @@
       <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="17" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1859,13 +1859,13 @@
       <c r="D16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1882,7 +1882,7 @@
       <c r="A18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -1899,7 +1899,7 @@
       <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1916,16 +1916,16 @@
       <c r="A20" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="17" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1933,68 +1933,68 @@
       <c r="A21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="12"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="12"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="12"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="12"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="17" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2002,133 +2002,133 @@
       <c r="A26" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="12"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="12"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="12"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="12"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="12"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="12"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="12"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="12"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="12"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="19" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2136,33 +2136,33 @@
       <c r="A36" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="16"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="16"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="19"/>
     </row>
     <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C38" s="5" t="s">
@@ -2179,7 +2179,7 @@
       <c r="A39" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C39" s="5" t="s">
@@ -2196,7 +2196,7 @@
       <c r="A40" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -2213,7 +2213,7 @@
       <c r="A41" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -2230,7 +2230,7 @@
       <c r="A42" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -2247,7 +2247,7 @@
       <c r="A43" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -2264,7 +2264,7 @@
       <c r="A44" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -2281,7 +2281,7 @@
       <c r="A45" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C45" s="5" t="s">
@@ -2298,7 +2298,7 @@
       <c r="A46" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -2315,16 +2315,16 @@
       <c r="A47" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="19" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2332,68 +2332,68 @@
       <c r="A48" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="16"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="19"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="11"/>
-      <c r="E49" s="16"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="16"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="16"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="19"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="17" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2401,189 +2401,189 @@
       <c r="A53" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="11"/>
-      <c r="E53" s="12"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="17"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="12"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="17"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="12"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D56" s="11"/>
-      <c r="E56" s="12"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="17"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="12"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="17"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="12"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="17"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="12"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="17"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="11"/>
-      <c r="E60" s="12"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="17"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="12"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="17"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="12"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="17"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="11"/>
-      <c r="E63" s="12"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="17"/>
     </row>
     <row r="64" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="13" t="s">
+      <c r="B64" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D64" s="11"/>
-      <c r="E64" s="12"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="17"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="19" t="s">
+      <c r="B65" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="12"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="17"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="11"/>
-      <c r="E66" s="12"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="17"/>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="19" t="s">
+      <c r="B67" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C67" s="5" t="s">
@@ -2600,7 +2600,7 @@
       <c r="A68" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C68" s="5" t="s">
@@ -2617,7 +2617,7 @@
       <c r="A69" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C69" s="5" t="s">
@@ -2634,7 +2634,7 @@
       <c r="A70" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C70" s="5" t="s">
@@ -2651,7 +2651,7 @@
       <c r="A71" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B71" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C71" s="5" t="s">
@@ -2668,7 +2668,7 @@
       <c r="A72" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C72" s="5" t="s">
@@ -2685,7 +2685,7 @@
       <c r="A73" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -2702,7 +2702,7 @@
       <c r="A74" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C74" s="5" t="s">
@@ -2719,7 +2719,7 @@
       <c r="A75" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B75" s="19" t="s">
+      <c r="B75" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C75" s="5" t="s">
@@ -2736,7 +2736,7 @@
       <c r="A76" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C76" s="5" t="s">
@@ -2753,7 +2753,7 @@
       <c r="A77" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="19" t="s">
+      <c r="B77" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C77" s="5" t="s">
@@ -2767,53 +2767,53 @@
       </c>
     </row>
     <row r="78" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B78" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C78" s="13" t="s">
+      <c r="B78" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C78" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="17" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B79" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C79" s="13" t="s">
+      <c r="B79" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C79" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D79" s="11"/>
-      <c r="E79" s="12"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="17"/>
     </row>
     <row r="80" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B80" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C80" s="13" t="s">
+      <c r="B80" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D80" s="11"/>
-      <c r="E80" s="12"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="17"/>
     </row>
     <row r="81" spans="1:5" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C81" s="5" t="s">
@@ -2830,7 +2830,7 @@
       <c r="A82" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C82" s="5" t="s">
@@ -2847,7 +2847,7 @@
       <c r="A83" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B83" s="19" t="s">
+      <c r="B83" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C83" s="5" t="s">
@@ -2864,7 +2864,7 @@
       <c r="A84" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C84" s="5" t="s">
@@ -2879,6 +2879,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="D25:D34"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="E25:E34"/>
+    <mergeCell ref="E35:E37"/>
     <mergeCell ref="E78:E80"/>
     <mergeCell ref="D78:D80"/>
     <mergeCell ref="D35:D37"/>
@@ -2886,16 +2896,6 @@
     <mergeCell ref="D52:D66"/>
     <mergeCell ref="E47:E51"/>
     <mergeCell ref="E52:E66"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="E20:E24"/>
-    <mergeCell ref="E25:E34"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="D20:D24"/>
-    <mergeCell ref="D25:D34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/游戏机制/生物生成/所有生物的spawnRules.xlsx
+++ b/游戏机制/生物生成/所有生物的spawnRules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\生物生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D5E50F-99CA-4137-9E07-78B088A1769E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A70DBA-AA4D-4A84-AC0E-4B85D972B420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpawnPlacements 代码解读" sheetId="1" r:id="rId1"/>
@@ -878,16 +878,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>非和平 and (1/20概率 or 水下不可见天空(此方块)) and 下方含水 and (此处含水 or 某种刷怪笼生成)
-水下不可见天空（此方块)：
-    如果：此方块 &gt;= 海平面，
-    那么：return 此处天空亮度 &lt; 15
-    否则(此方块 &lt; 海平面)：
-        此方块海平面高度处天空亮度 &lt; 15
-        or “海平面下方方块 ~ 生成点上方方块”的范围不存在“不完全透光 and 不是流体(包含气泡柱)”的方块</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>溺尸自然生成群系及其权重：
     河流(river) 100/615 ≈ 1/6 (1只)
     溶洞(dripstone_caves) 95/610 ≈ 1/6 (4只)
@@ -929,6 +919,13 @@
   <si>
     <t>下方含水 and 上方是水方块
 and 海平面-25 &lt;= y &lt;= 海平面-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	非和平 and (1/20概率 or !canSeeSkyFromBelowWater(此方块)) and 下方含水 and (此处含水 or 来自刷怪笼)
+	考虑实际守卫者在海底神殿内生成，海底神殿区域总是为y=39~61，
+	!canSeeSkyFromBelowWater(此方块)此部分可简化为：
+		return 此方块的海平面y63处天空亮度&lt;15 or “y=62 ~ y=此方块+1”存在“亮度衰减&gt;0”的方块</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1609,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -1666,7 +1663,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
@@ -1700,7 +1697,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1730,7 +1727,7 @@
         <v>200</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
@@ -2862,19 +2859,19 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C84" s="5" t="s">
+      <c r="D84" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/游戏机制/生物生成/所有生物的spawnRules.xlsx
+++ b/游戏机制/生物生成/所有生物的spawnRules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\生物生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A70DBA-AA4D-4A84-AC0E-4B85D972B420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC49466-3E97-4F1F-9C90-7648ACC5ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,9 +1087,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1098,6 +1095,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1693,10 +1693,10 @@
       <c r="C6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="20" t="s">
         <v>213</v>
       </c>
     </row>
@@ -1710,8 +1710,8 @@
       <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" customFormat="1" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
@@ -1740,7 +1740,7 @@
       <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1757,7 +1757,7 @@
       <c r="C10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="19"/>
+      <c r="D10" s="18"/>
       <c r="E10" s="7" t="s">
         <v>27</v>
       </c>
@@ -1772,7 +1772,7 @@
       <c r="C11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="7" t="s">
@@ -1789,7 +1789,7 @@
       <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="19"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="7" t="s">
         <v>27</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="19"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="7" t="s">
         <v>27</v>
       </c>
@@ -1839,7 +1839,7 @@
       <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="D16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1919,10 +1919,10 @@
       <c r="C20" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="20" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1936,8 +1936,8 @@
       <c r="C21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="17"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
@@ -1949,8 +1949,8 @@
       <c r="C22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="17"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="20"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1962,8 +1962,8 @@
       <c r="C23" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="17"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -1975,8 +1975,8 @@
       <c r="C24" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="17"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -1988,10 +1988,10 @@
       <c r="C25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="20" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2005,8 +2005,8 @@
       <c r="C26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="20"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
@@ -2018,8 +2018,8 @@
       <c r="C27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="20"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -2031,8 +2031,8 @@
       <c r="C28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="20"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -2044,8 +2044,8 @@
       <c r="C29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="20"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -2057,8 +2057,8 @@
       <c r="C30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="20"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
@@ -2070,8 +2070,8 @@
       <c r="C31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="20"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
@@ -2083,8 +2083,8 @@
       <c r="C32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="20"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -2096,8 +2096,8 @@
       <c r="C33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="20"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
@@ -2109,8 +2109,8 @@
       <c r="C34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
@@ -2122,10 +2122,10 @@
       <c r="C35" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="18" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2139,8 +2139,8 @@
       <c r="C36" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="19"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
@@ -2152,8 +2152,8 @@
       <c r="C37" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="18"/>
-      <c r="E37" s="19"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -2318,10 +2318,10 @@
       <c r="C47" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="18" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2335,8 +2335,8 @@
       <c r="C48" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="18"/>
-      <c r="E48" s="19"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="18"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -2348,8 +2348,8 @@
       <c r="C49" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D49" s="18"/>
-      <c r="E49" s="19"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="18"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
@@ -2361,8 +2361,8 @@
       <c r="C50" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D50" s="18"/>
-      <c r="E50" s="19"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="18"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -2374,8 +2374,8 @@
       <c r="C51" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="18"/>
-      <c r="E51" s="19"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="18"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
@@ -2387,10 +2387,10 @@
       <c r="C52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="20" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2404,8 +2404,8 @@
       <c r="C53" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="20"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
@@ -2417,8 +2417,8 @@
       <c r="C54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D54" s="18"/>
-      <c r="E54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="20"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
@@ -2430,8 +2430,8 @@
       <c r="C55" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="20"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
@@ -2443,8 +2443,8 @@
       <c r="C56" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="20"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -2456,8 +2456,8 @@
       <c r="C57" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="18"/>
-      <c r="E57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="20"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
@@ -2469,8 +2469,8 @@
       <c r="C58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D58" s="18"/>
-      <c r="E58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="20"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
@@ -2482,8 +2482,8 @@
       <c r="C59" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="20"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
@@ -2495,8 +2495,8 @@
       <c r="C60" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="18"/>
-      <c r="E60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="20"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -2508,8 +2508,8 @@
       <c r="C61" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D61" s="18"/>
-      <c r="E61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="20"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
@@ -2521,8 +2521,8 @@
       <c r="C62" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="18"/>
-      <c r="E62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="20"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
@@ -2534,8 +2534,8 @@
       <c r="C63" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D63" s="18"/>
-      <c r="E63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="20"/>
     </row>
     <row r="64" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
@@ -2547,8 +2547,8 @@
       <c r="C64" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D64" s="18"/>
-      <c r="E64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="20"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
@@ -2560,8 +2560,8 @@
       <c r="C65" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="18"/>
-      <c r="E65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="20"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
@@ -2573,8 +2573,8 @@
       <c r="C66" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="18"/>
-      <c r="E66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="20"/>
     </row>
     <row r="67" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
@@ -2773,10 +2773,10 @@
       <c r="C78" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="D78" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="20" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2790,8 +2790,8 @@
       <c r="C79" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D79" s="18"/>
-      <c r="E79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="20"/>
     </row>
     <row r="80" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
@@ -2803,8 +2803,8 @@
       <c r="C80" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D80" s="18"/>
-      <c r="E80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="20"/>
     </row>
     <row r="81" spans="1:5" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
@@ -2876,16 +2876,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="D20:D24"/>
-    <mergeCell ref="D25:D34"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="E20:E24"/>
-    <mergeCell ref="E25:E34"/>
-    <mergeCell ref="E35:E37"/>
     <mergeCell ref="E78:E80"/>
     <mergeCell ref="D78:D80"/>
     <mergeCell ref="D35:D37"/>
@@ -2893,6 +2883,16 @@
     <mergeCell ref="D52:D66"/>
     <mergeCell ref="E47:E51"/>
     <mergeCell ref="E52:E66"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="E25:E34"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="D25:D34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
